--- a/fiyat-listesi.xlsx
+++ b/fiyat-listesi.xlsx
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>2397.31</v>
+        <v>1918.76</v>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>GN 600 NMV TEK INOX KAPI DIK TIP BUZDOLABI HİDROKARBON</t>
+          <t>GN 600 NMV TEK INOX KAPI DIK TIP BUZDOLABI K TİP</t>
         </is>
       </c>
       <c r="F75" s="8" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.06NMV.00</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>3168.83</v>
+        <v>2825.29</v>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>GN 1200 NMV CIFT INOX KAPI DIK TIP BUZDOLABI HC K TİP</t>
+          <t>GN 1200 NMV CIFT INOX KAPI DIK TIP BUZDOLABI K TİP</t>
         </is>
       </c>
       <c r="F76" s="8" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.12NMV.00</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>2574.24</v>
+        <v>2141.66</v>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>GN 600 LMV TEK INOX KAPI DIK TIP DERIN DONDURUCU HİDROKARBON</t>
+          <t>GN 600 LMV TEK INOX KAPI DIK TIP DERIN DONDURUCU - K TİP</t>
         </is>
       </c>
       <c r="F77" s="8" t="n">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.06LMV.00</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>3530.75</v>
+        <v>3385.41</v>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>GN 1200 LMV TEK INOX KAPI DIK TIP FREEZER 290 GAZLI K TIP</t>
+          <t>GN 1200 LMV CIFT INOX KAPI DIK TIP DERİNDONDURUCU K 430 TİP</t>
         </is>
       </c>
       <c r="F78" s="8" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.12LMV.00</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>2517.95</v>
+        <v>2121.55</v>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>GN 600 NMV TEK CAM KAPI DIK TIP BUZDOLABI</t>
+          <t>GN 600 NMV TEK CAM KAPILI BUZDOLABI 430 K TIP</t>
         </is>
       </c>
       <c r="F79" s="8" t="n">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.06NMV.01</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>3692.76</v>
+        <v>3034.4</v>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>GN 1200 NMV CIFT CAM KAPI DIK TIP BUZDOLABI</t>
+          <t>GN 1200 NMV IKI CAM KAPILI BUZDOLABI 430 K TIP</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.12NMV.01</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>2087.09</v>
+        <v>1840.63</v>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>TAG 270 NMV CIFT INOX KAPI YATAY TIP BUZDOLABI HIDROKARBON 304</t>
+          <t>TAG 270 NMV CIFT INOX KAPI YATAY TIP BUZDOLABI</t>
         </is>
       </c>
       <c r="F81" s="8" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.27NMV.00</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>1925.66</v>
+        <v>1876.83</v>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.27NMV.01</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>2525.41</v>
+        <v>2500.14</v>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.27NMV.02</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="C84" s="8" t="n">
-        <v>3163.09</v>
+        <v>2872.4</v>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.27NMV.03</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>2673.63</v>
+        <v>2307.11</v>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>TAG 370 NMV 3 INOX KAPI YATAY TIP BUZDOLABI HİDROKARBON</t>
+          <t>TAG 370 NMV 3 INOX KAPI YATAY TIP BUZDOLABI</t>
         </is>
       </c>
       <c r="F85" s="8" t="n">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.37NMV.00</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>2233.58</v>
+        <v>2360.54</v>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.37NMV.01</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>3678.97</v>
+        <v>3292.34</v>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.37NMV.02</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="C88" s="8" t="n">
-        <v>4223</v>
+        <v>3854.19</v>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.37NMV.03</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>3111.96</v>
+        <v>2727.63</v>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>TAG 470 NMV 4 INOX KAPI YATAY TIP BUZDOLABI HİDROKARBON</t>
+          <t>TAG 470 NMV 4 INOX KAPI YATAY TIP BUZDOLABI</t>
         </is>
       </c>
       <c r="F89" s="8" t="n">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.47NMV.00</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>3144.13</v>
+        <v>2798.29</v>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.47NMV.01</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>4556.78</v>
+        <v>4047.21</v>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.47NMV.02</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>5282.34</v>
+        <v>4795.18</v>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.47NMV.03</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>2038.83</v>
+        <v>1948.64</v>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.27LMV.00</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>2778.76</v>
+        <v>2685.12</v>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.27LMV.02</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>3418.73</v>
+        <v>3019.47</v>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.27LMV.03</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>2407.07</v>
+        <v>2399.03</v>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>TAG 370 LMV 3 INOX KAPI YATAY TIP BUZDOLABI HİDROKARBON 430</t>
+          <t>TAG 370 LMV 3 INOX KAPI YATAY TIP DERIN DONDURUCU</t>
         </is>
       </c>
       <c r="F96" s="8" t="n">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.37LMV.00</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>3950.7</v>
+        <v>3534.2</v>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.37LMV.02</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>4476.35</v>
+        <v>4091.45</v>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.37LMV.03</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>3207.9</v>
+        <v>2835.63</v>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.47LMV.00</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>4914.68</v>
+        <v>4318.37</v>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.47LMV.02</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>5587.39</v>
+        <v>5036.47</v>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.47LMV.03</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>1023.72</v>
+        <v>946.74</v>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>PZC 35 TEZGAH USTU CAMLI PIZZA HAZIRLIK UNITESI</t>
+          <t>PZC 35 TEZGAH USTU CAMLI PIZZA HAZIRLIK UNITESI -430</t>
         </is>
       </c>
       <c r="F102" s="8" t="n">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.PZC35.00</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>957.66</v>
+        <v>860</v>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>PZC 35 YUKSEK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI</t>
+          <t>PZC 35 YUKSEK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI -430</t>
         </is>
       </c>
       <c r="F103" s="8" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.PZC35.H0</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>926.0599999999999</v>
+        <v>864.59</v>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>PZC 35 ALCAK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI HC</t>
+          <t>PZC 35 ALCAK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI -430</t>
         </is>
       </c>
       <c r="F104" s="8" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.PZC35.L0</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>1140.34</v>
+        <v>1027.74</v>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>PZC 54 TEZGAH USTU CAMLI PIZZA HAZIRLIK UNITESI</t>
+          <t>PZC 54 TEZGAH USTU CAMLI PIZZA HAZIRLIK UNITESI -430</t>
         </is>
       </c>
       <c r="F105" s="8" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.PZC54.00</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>1082.32</v>
+        <v>953.64</v>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>PZC 54 YUKSEK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI</t>
+          <t>PZC 54 YUKSEK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI -430</t>
         </is>
       </c>
       <c r="F106" s="8" t="n">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.PZC54.H0</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>1049</v>
+        <v>915.72</v>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>PZC 54 ALCAK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI</t>
+          <t>PZC 54 ALCAK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI -430</t>
         </is>
       </c>
       <c r="F107" s="8" t="n">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.PZC54.L0</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>1301.2</v>
+        <v>1158.15</v>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>PZC 72 TEZGAH USTU CAMLI PIZZA HAZIRLIK UNITESI</t>
+          <t>PZC 72 TEZGAH USTU CAMLI PIZZA HAZIRLIK UNITESI -430</t>
         </is>
       </c>
       <c r="F108" s="8" t="n">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.PZC72.00</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>1418.97</v>
+        <v>1262.71</v>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>PZC 72 YUKSEK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI</t>
+          <t>PZC 72 YUKSEK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI -430</t>
         </is>
       </c>
       <c r="F109" s="8" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.PZC72.H0</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="C110" s="8" t="n">
-        <v>1375.88</v>
+        <v>1217.9</v>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>PZC 72 ALCAK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI</t>
+          <t>PZC 72 ALCAK PLEXIGLASS KAPAKLI  PIZZA HAZIRLIK UNITESI -430</t>
         </is>
       </c>
       <c r="F110" s="8" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79E4.PZC72.L0</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>2459.35</v>
+        <v>2058.94</v>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>GN 600 NMV CIFT YARIM INOX KAPI DIK TIP BUZDOLABI</t>
+          <t>GN 600 NMV IKI YARIM KAPILI BUZDOLABI 430 K TIP</t>
         </is>
       </c>
       <c r="F111" s="8" t="n">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.06NMV.10</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>3716.31</v>
+        <v>3101.04</v>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>GN 1200 NMV 4 YARIM INOX KAPI DIK TIP BUZDOLABI</t>
+          <t>GN 1200 NMV DORT YARIM KAPILI BUZDOLABI 430 K TIP</t>
         </is>
       </c>
       <c r="F112" s="8" t="n">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.12NMV.10</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>2697.76</v>
+        <v>2290.45</v>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>GN 600 NMV CIFT YARIM CAM KAPI DIK TIP BUZDOLABI</t>
+          <t>GN 600 NMV IKI YARIM  CAM KAPILI BUZDOLABI 430 K TIP</t>
         </is>
       </c>
       <c r="F113" s="8" t="n">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.06NMV.11</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="C114" s="8" t="n">
-        <v>2559.31</v>
+        <v>2301.37</v>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>GN 600 LMV IKI YARIM KAPILI DERIN DONDURUCU HIDROKARBON K TIP</t>
+          <t>GN 600 LMV IKI YARIM KAPILI DERIN DONDURUCU 430 K TIP</t>
         </is>
       </c>
       <c r="F114" s="8" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.06LMV.10</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>3994.36</v>
+        <v>3414.13</v>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>GN 1200 NMV 4 YARIM CAM KAPI DIK TIP BUZDOLABI</t>
+          <t>GN 1200 NMV DORT YARIM CAM KAPILI BUZDOLABI 430 K TIP</t>
         </is>
       </c>
       <c r="F115" s="8" t="n">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.12NMV.11</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="C116" s="8" t="n">
-        <v>4164.41</v>
+        <v>3695.63</v>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>GN 1200 LMV 4 YARIM INOX KAPI DIK TIP DERIN DONDURUCU</t>
+          <t>GN 1200 LMV DORT YARIM KAPILI DERIN DONDURUCU 430 K TIP</t>
         </is>
       </c>
       <c r="F116" s="8" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>ÖZTİRYAKİLER × 0.25 × 1.067 × 2.03</t>
+          <t>ÖZTİRYAKİLER 79K4.12LMV.10</t>
         </is>
       </c>
     </row>
